--- a/artfynd/A 40720-2025 artfynd.xlsx
+++ b/artfynd/A 40720-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>267863</v>
       </c>
       <c r="B2" t="n">
-        <v>96679</v>
+        <v>96682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40720-2025 artfynd.xlsx
+++ b/artfynd/A 40720-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>267863</v>
       </c>
       <c r="B2" t="n">
-        <v>96682</v>
+        <v>96683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40720-2025 artfynd.xlsx
+++ b/artfynd/A 40720-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>267863</v>
       </c>
       <c r="B2" t="n">
-        <v>96683</v>
+        <v>96688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
